--- a/artfynd/A 2018-2024 artfynd.xlsx
+++ b/artfynd/A 2018-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2018-2024 artfynd.xlsx
+++ b/artfynd/A 2018-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,6 +803,216 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123990725</v>
+      </c>
+      <c r="B3" t="n">
+        <v>95323</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bondrum-Tjörnerödsmölla, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>440227</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6169341</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fågeltofta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123990765</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57399</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100082</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Röd glada</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Milvus milvus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bondrum-Tjörnerödsmölla, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>440034</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6169376</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tomelilla</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fågeltofta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2018-2024 artfynd.xlsx
+++ b/artfynd/A 2018-2024 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123990725</v>
+        <v>123990765</v>
       </c>
       <c r="B3" t="n">
-        <v>95345</v>
+        <v>57421</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,21 +822,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>100082</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440227</v>
+        <v>440034</v>
       </c>
       <c r="R3" t="n">
-        <v>6169341</v>
+        <v>6169376</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -884,13 +884,17 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123990765</v>
+        <v>123990725</v>
       </c>
       <c r="B4" t="n">
-        <v>57421</v>
+        <v>95345</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100082</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440034</v>
+        <v>440227</v>
       </c>
       <c r="R4" t="n">
-        <v>6169376</v>
+        <v>6169341</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -987,17 +991,13 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2018-2024 artfynd.xlsx
+++ b/artfynd/A 2018-2024 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123990765</v>
+        <v>123990725</v>
       </c>
       <c r="B3" t="n">
-        <v>57421</v>
+        <v>95345</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,21 +822,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100082</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440034</v>
+        <v>440227</v>
       </c>
       <c r="R3" t="n">
-        <v>6169376</v>
+        <v>6169341</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -884,17 +884,13 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -913,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123990725</v>
+        <v>123990765</v>
       </c>
       <c r="B4" t="n">
-        <v>95345</v>
+        <v>57421</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>100082</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440227</v>
+        <v>440034</v>
       </c>
       <c r="R4" t="n">
-        <v>6169341</v>
+        <v>6169376</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -991,13 +987,17 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2018-2024 artfynd.xlsx
+++ b/artfynd/A 2018-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>63295754</v>
       </c>
       <c r="B2" t="n">
-        <v>104790</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440191.5401657217</v>
+        <v>440192</v>
       </c>
       <c r="R2" t="n">
-        <v>6169574.260234257</v>
+        <v>6169574</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>2000-07-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2000-07-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 2018-2024 artfynd.xlsx
+++ b/artfynd/A 2018-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63295754</v>
       </c>
       <c r="B2" t="n">
-        <v>107233</v>
+        <v>107245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2018-2024 artfynd.xlsx
+++ b/artfynd/A 2018-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63295754</v>
       </c>
       <c r="B2" t="n">
-        <v>107245</v>
+        <v>107254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2018-2024 artfynd.xlsx
+++ b/artfynd/A 2018-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63295754</v>
       </c>
       <c r="B2" t="n">
-        <v>107254</v>
+        <v>107259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2018-2024 artfynd.xlsx
+++ b/artfynd/A 2018-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63295754</v>
       </c>
       <c r="B2" t="n">
-        <v>107259</v>
+        <v>107287</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2018-2024 artfynd.xlsx
+++ b/artfynd/A 2018-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63295754</v>
       </c>
       <c r="B2" t="n">
-        <v>107287</v>
+        <v>107293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2018-2024 artfynd.xlsx
+++ b/artfynd/A 2018-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63295754</v>
       </c>
       <c r="B2" t="n">
-        <v>107293</v>
+        <v>107300</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2018-2024 artfynd.xlsx
+++ b/artfynd/A 2018-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63295754</v>
       </c>
       <c r="B2" t="n">
-        <v>107300</v>
+        <v>107304</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2018-2024 artfynd.xlsx
+++ b/artfynd/A 2018-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63295754</v>
       </c>
       <c r="B2" t="n">
-        <v>107304</v>
+        <v>107312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2018-2024 artfynd.xlsx
+++ b/artfynd/A 2018-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63295754</v>
       </c>
       <c r="B2" t="n">
-        <v>107315</v>
+        <v>107320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2018-2024 artfynd.xlsx
+++ b/artfynd/A 2018-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63295754</v>
       </c>
       <c r="B2" t="n">
-        <v>107320</v>
+        <v>107328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2018-2024 artfynd.xlsx
+++ b/artfynd/A 2018-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>63295754</v>
       </c>
       <c r="B2" t="n">
-        <v>107328</v>
+        <v>107338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2018-2024 artfynd.xlsx
+++ b/artfynd/A 2018-2024 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63295754</v>
+        <v>123990725</v>
       </c>
       <c r="B2" t="n">
-        <v>107338</v>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1855</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Åkerkulla</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anthemis arvensis</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>ca 1 km O Kristianstadsv., Sk</t>
+          <t>Bondrum-Tjörnerödsmölla, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440192</v>
+        <v>440227</v>
       </c>
       <c r="R2" t="n">
-        <v>6169574</v>
+        <v>6169341</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2000-07-12</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-07-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Anthemis arvensis/2D4h2445/Fågeltofta s:n/BSl/ /Bengt Sandkull,Lund</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,47 +754,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>skogsväg</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>SkFlora    630470</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Lars Salomon</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Sandkull</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Skånes Flora (1989-2006)</t>
-        </is>
-      </c>
+          <t>Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>123990765</v>
       </c>
       <c r="B3" t="n">
-        <v>57421</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57890</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,53 +875,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123990725</v>
+        <v>133897843</v>
       </c>
       <c r="B4" t="n">
-        <v>95345</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111210</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>221049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Valeriana dioica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bondrum-Tjörnerödsmölla, Sk</t>
+          <t>Braskaängen, Småvänderot, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440227</v>
+        <v>440168</v>
       </c>
       <c r="R4" t="n">
-        <v>6169341</v>
+        <v>6169561</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,14 +947,19 @@
           <t>Fågeltofta</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>M-Tom-0213</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -982,22 +968,25 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
+          <t>Charlotte Wigermo</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars Salomon</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Klas Fregert, Ola Eriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2018-2024 artfynd.xlsx
+++ b/artfynd/A 2018-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123990725</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123990765</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,8 +1002,18 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133897843</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>